--- a/AfterToken/Configs/GameConfig/Datas/battle.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/battle.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Enemy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Wave" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Drop" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Wave" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Drop" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,42 +430,32 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>levelId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>maxHp</t>
+          <t>waveIndex</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>moveSpeed</t>
+          <t>enemyId</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>rotationSpeed</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>attackDamage</t>
+          <t>spawnInterval</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>attackRange</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>attackInterval</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>prefab</t>
+          <t>spawnRadius</t>
         </is>
       </c>
     </row>
@@ -483,7 +472,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -493,32 +482,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>float</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
@@ -530,114 +509,153 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>波次ID</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>关卡ID</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>波次索引</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>敌人ID</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>最大血量</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>移动速度</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>旋转速度</t>
+          <t>数量</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>攻击力</t>
+          <t>生成间隔</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>攻击范围</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>攻击间隔</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>预制体</t>
+          <t>生成半径</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>9001</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Training Dummy</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
-        <v>360</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Enemy_Dummy</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>9002</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Assault Bot</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>80</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9001</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>360</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Enemy_Assault</t>
-        </is>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9002</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -651,261 +669,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>levelId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>waveIndex</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>enemyId</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>spawnInterval</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>spawnRadius</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>波次ID</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>关卡ID</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>波次索引</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>敌人ID</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>生成间隔</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>生成半径</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9001</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9002</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>9001</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9002</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/AfterToken/Configs/GameConfig/Datas/battle.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/battle.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,6 +823,46 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E7" t="n">
+        <v>800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
